--- a/Bridgewater_Bottom_Up_Energy_Model.xlsx
+++ b/Bridgewater_Bottom_Up_Energy_Model.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="472">
   <si>
     <t xml:space="preserve">Bridgewater bottom-up energy model</t>
   </si>
@@ -1077,16 +1077,19 @@
     <t xml:space="preserve">People (occupants)</t>
   </si>
   <si>
-    <t xml:space="preserve">138 beds × 100% × 8760h = 1.65M person-h</t>
+    <t xml:space="preserve">Engine State 2 integration with 1.5/room canonical density</t>
   </si>
   <si>
     <t xml:space="preserve">Lighting</t>
   </si>
   <si>
-    <t xml:space="preserve">LPD × GIA × annual hours</t>
+    <t xml:space="preserve">Engine State 2 integration, current LPD 1.5 W/m² (flagged for BRUKL ingestion)</t>
   </si>
   <si>
     <t xml:space="preserve">Equipment (small power)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine State 2 integration, current EPD 1.5 W/m² peak (flagged)</t>
   </si>
   <si>
     <t xml:space="preserve">Refrigeration waste heat</t>
@@ -2389,7 +2392,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -2400,7 +2403,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2411,7 +2414,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C5" s="25" t="n">
         <f aca="false">i_water_total</f>
@@ -2423,7 +2426,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C6" s="29" t="n">
         <f aca="false">i_hot_frac</f>
@@ -2435,7 +2438,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">C5*C6</f>
@@ -2447,19 +2450,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">C7*i_rho_w</f>
         <v>4600000</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">i_T_delivery-i_T_cold</f>
@@ -2471,7 +2474,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">C8*i_cp_w*C9/3600</f>
@@ -2483,7 +2486,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">C10*i_dist_loss</f>
@@ -2497,12 +2500,12 @@
         <v>53411.1111111111</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">C10+C11</f>
@@ -2514,7 +2517,7 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -2525,19 +2528,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>155</v>
@@ -2545,7 +2548,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C16" s="35" t="n">
         <f aca="false">i_ashp_share</f>
@@ -2564,12 +2567,12 @@
         <v>53411.1111111111</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">1-i_ashp_share</f>
@@ -2588,12 +2591,12 @@
         <v>178037.037037037</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>256</v>
@@ -2609,12 +2612,12 @@
         <v>1500</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">F16+F18</f>
@@ -2623,7 +2626,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">F17</f>
@@ -2632,14 +2635,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F22" s="13" t="n">
         <f aca="false">F21/1000</f>
         <v>178.037037037037</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -2670,7 +2673,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -2681,7 +2684,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2692,13 +2695,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>320</v>
@@ -2712,7 +2715,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">i_wc_flow</f>
@@ -2733,7 +2736,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C7" s="25" t="n">
         <f aca="false">i_mvhr_flow</f>
@@ -2754,7 +2757,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">F6+F7</f>
@@ -2763,7 +2766,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -2774,13 +2777,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>109</v>
@@ -2794,19 +2797,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C12" s="23" t="n">
         <f aca="false">i_mvhr_flow*i_rho_air/1000</f>
         <v>1.74</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">i_mvhr_hre*(i_mvhr_flow*i_rho_air/1000)*i_cp_air*04_Weather!$C$16/1000</f>
@@ -2817,12 +2820,12 @@
         <v>120.76941888</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">E13*i_mvhr_useful_frac</f>
@@ -2833,7 +2836,7 @@
         <v>66423.180384</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2867,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -2875,7 +2878,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2886,19 +2889,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>155</v>
@@ -2906,7 +2909,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">i_vrf_h_share</f>
@@ -2914,7 +2917,7 @@
       </c>
       <c r="D6" s="25" t="n">
         <f aca="false">08_Heat_Balance!$C$11*C6</f>
-        <v>0</v>
+        <v>51373.8172216928</v>
       </c>
       <c r="E6" s="29" t="n">
         <f aca="false">i_vrf_h_scop</f>
@@ -2922,12 +2925,12 @@
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">D6/E6</f>
-        <v>0</v>
+        <v>10033.9486761119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">i_panel_share</f>
@@ -2935,7 +2938,7 @@
       </c>
       <c r="D7" s="36" t="n">
         <f aca="false">08_Heat_Balance!$C$11*C7</f>
-        <v>0</v>
+        <v>2703.8851169312</v>
       </c>
       <c r="E7" s="29" t="n">
         <f aca="false">i_panel_cop</f>
@@ -2943,21 +2946,21 @@
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">D7/E7</f>
-        <v>0</v>
+        <v>2703.8851169312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F8" s="12" t="n">
         <f aca="false">F6+F7</f>
-        <v>0</v>
+        <v>12737.8337930431</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -2968,19 +2971,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>155</v>
@@ -2988,7 +2991,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C12" s="35" t="n">
         <f aca="false">i_vrf_c_share</f>
@@ -2996,7 +2999,7 @@
       </c>
       <c r="D12" s="36" t="n">
         <f aca="false">08_Heat_Balance!$C$19*C12</f>
-        <v>433696.318675267</v>
+        <v>183964.728242767</v>
       </c>
       <c r="E12" s="29" t="n">
         <f aca="false">i_vrf_c_seer</f>
@@ -3004,12 +3007,12 @@
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">D12/E12</f>
-        <v>123560.204750788</v>
+        <v>52411.6034879677</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C13" s="35" t="n">
         <f aca="false">i_dx_share</f>
@@ -3017,7 +3020,7 @@
       </c>
       <c r="D13" s="36" t="n">
         <f aca="false">08_Heat_Balance!$C$19*C13</f>
-        <v>22826.1220355404</v>
+        <v>9682.35411804036</v>
       </c>
       <c r="E13" s="29" t="n">
         <f aca="false">i_dx_seer</f>
@@ -3025,16 +3028,16 @@
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">D13/E13</f>
-        <v>4061.58755080789</v>
+        <v>1722.83881103921</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">F12+F13</f>
-        <v>127621.792301596</v>
+        <v>54134.442299007</v>
       </c>
     </row>
   </sheetData>
@@ -3065,7 +3068,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -3073,7 +3076,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -3081,7 +3084,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>109</v>
@@ -3095,7 +3098,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">i_light_LPD*(i_length*i_width*i_floors)*i_light_h/1000</f>
@@ -3106,7 +3109,7 @@
         <v>151.435872</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3122,12 +3125,12 @@
         <v>388.962</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C8" s="25" t="n">
         <f aca="false">i_refrig</f>
@@ -3143,7 +3146,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">i_ext_light</f>
@@ -3159,7 +3162,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">i_lifts</f>
@@ -3170,12 +3173,12 @@
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C11" s="25" t="n">
         <f aca="false">i_pumps</f>
@@ -3191,7 +3194,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C12" s="25" t="n">
         <f aca="false">i_other_elec</f>
@@ -3202,12 +3205,12 @@
         <v>5</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">C6+C7+C8+C9+C10+C11+C12</f>
@@ -3246,7 +3249,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -3256,7 +3259,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -3266,7 +3269,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>109</v>
@@ -3275,7 +3278,7 @@
         <v>139</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>155</v>
@@ -3283,41 +3286,41 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">11_Systems!$F$8</f>
-        <v>0</v>
+        <v>12737.8337930431</v>
       </c>
       <c r="D6" s="13" t="n">
         <f aca="false">C6/1000</f>
-        <v>0</v>
+        <v>12.7378337930431</v>
       </c>
       <c r="E6" s="17" t="n">
         <f aca="false">C6/C18</f>
-        <v>0</v>
+        <v>0.0177161590384853</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C7" s="25" t="n">
         <f aca="false">11_Systems!$F$14</f>
-        <v>127621.792301596</v>
+        <v>54134.442299007</v>
       </c>
       <c r="D7" s="13" t="n">
         <f aca="false">C7/1000</f>
-        <v>127.621792301596</v>
+        <v>54.134442299007</v>
       </c>
       <c r="E7" s="17" t="n">
         <f aca="false">C7/C18</f>
-        <v>0.163671244185673</v>
+        <v>0.0752917964554313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C8" s="25" t="n">
         <f aca="false">09_DHW!$F$20</f>
@@ -3329,12 +3332,12 @@
       </c>
       <c r="E8" s="17" t="n">
         <f aca="false">C8/C18</f>
-        <v>0.0704219061109431</v>
+        <v>0.0763720105969428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">10_Ventilation!$F$8</f>
@@ -3346,12 +3349,12 @@
       </c>
       <c r="E9" s="17" t="n">
         <f aca="false">C9/C18</f>
-        <v>0.0331056646653622</v>
+        <v>0.0359028363796161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">12_Other_Loads!$C$6</f>
@@ -3363,7 +3366,7 @@
       </c>
       <c r="E10" s="17" t="n">
         <f aca="false">C10/C18</f>
-        <v>0.194212110154422</v>
+        <v>0.210621526083107</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3380,12 +3383,12 @@
       </c>
       <c r="E11" s="17" t="n">
         <f aca="false">C11/C18</f>
-        <v>0.4988324747117</v>
+        <v>0.540979947131268</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C12" s="25" t="n">
         <f aca="false">i_refrig</f>
@@ -3397,12 +3400,12 @@
       </c>
       <c r="E12" s="17" t="n">
         <f aca="false">C12/C18</f>
-        <v>0.0102597677862969</v>
+        <v>0.0111266385329419</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C13" s="25" t="n">
         <f aca="false">i_ext_light</f>
@@ -3414,12 +3417,12 @@
       </c>
       <c r="E13" s="17" t="n">
         <f aca="false">C13/C18</f>
-        <v>0.00769482583972264</v>
+        <v>0.00834497889970642</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C14" s="25" t="n">
         <f aca="false">i_lifts</f>
@@ -3431,12 +3434,12 @@
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">C14/C18</f>
-        <v>0.0102597677862969</v>
+        <v>0.0111266385329419</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C15" s="25" t="n">
         <f aca="false">i_pumps</f>
@@ -3448,12 +3451,12 @@
       </c>
       <c r="E15" s="17" t="n">
         <f aca="false">C15/C18</f>
-        <v>0.00512988389314843</v>
+        <v>0.00556331926647095</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C16" s="25" t="n">
         <f aca="false">i_other_elec</f>
@@ -3465,25 +3468,25 @@
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">C16/C18</f>
-        <v>0.00641235486643553</v>
+        <v>0.00695414908308868</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16</f>
-        <v>779744.743412707</v>
+        <v>718995.227203161</v>
       </c>
       <c r="D18" s="26" t="n">
         <f aca="false">C18/1000</f>
-        <v>779.744743412707</v>
+        <v>718.995227203161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -3493,7 +3496,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>109</v>
@@ -3502,7 +3505,7 @@
         <v>139</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>155</v>
@@ -3510,7 +3513,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C22" s="25" t="n">
         <f aca="false">09_DHW!$F$21</f>
@@ -3527,7 +3530,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">C22</f>
@@ -3540,7 +3543,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -3550,13 +3553,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E27" s="16"/>
       <c r="F27" s="16" t="s">
@@ -3565,11 +3568,11 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C28" s="26" t="n">
         <f aca="false">13_Energy_Use!$C$18/1000</f>
-        <v>779.744743412707</v>
+        <v>718.995227203161</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>139</v>
@@ -3577,7 +3580,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C29" s="26" t="n">
         <f aca="false">13_Energy_Use!$C$24/1000</f>
@@ -3589,11 +3592,11 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C30" s="26" t="n">
         <f aca="false">(13_Energy_Use!$C$18+13_Energy_Use!$C$24)/1000</f>
-        <v>957.781780449744</v>
+        <v>897.032264240198</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>139</v>
@@ -3601,11 +3604,11 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C31" s="37" t="n">
         <f aca="false">(13_Energy_Use!$C$18+13_Energy_Use!$C$24)/(i_length*i_width*i_floors)</f>
-        <v>221.616405305601</v>
+        <v>207.5598741821</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>212</v>
@@ -3613,50 +3616,50 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C32" s="13" t="n">
         <f aca="false">13_Energy_Use!$C$18*i_cf_elec/1000</f>
-        <v>161.40716188643</v>
+        <v>148.832012031054</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C33" s="13" t="n">
         <f aca="false">13_Energy_Use!$C$24*i_cf_gas/1000</f>
         <v>32.5807777777778</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C34" s="26" t="n">
         <f aca="false">(13_Energy_Use!$C$18*i_cf_elec+13_Energy_Use!$C$24*i_cf_gas)/1000</f>
-        <v>193.987939664208</v>
+        <v>181.412789808832</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C35" s="26" t="n">
         <f aca="false">(13_Energy_Use!$C$18*i_cf_elec+13_Energy_Use!$C$24*i_cf_gas)/(i_length*i_width*i_floors)</f>
-        <v>44.8859131991782</v>
+        <v>41.9762112566135</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -3687,7 +3690,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -3698,7 +3701,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -3709,31 +3712,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C6" s="38" t="n">
         <f aca="false">13_Energy_Use!$C$18/1000</f>
-        <v>779.744743412707</v>
+        <v>718.995227203161</v>
       </c>
       <c r="D6" s="39" t="n">
         <f aca="false">i_m_elec</f>
@@ -3741,11 +3744,11 @@
       </c>
       <c r="E6" s="40" t="n">
         <f aca="false">C6-D6</f>
-        <v>219.744743412707</v>
+        <v>158.995227203161</v>
       </c>
       <c r="F6" s="41" t="n">
         <f aca="false">(C6-D6)/D6</f>
-        <v>0.392401327522691</v>
+        <v>0.283920048577073</v>
       </c>
       <c r="G6" s="42" t="str">
         <f aca="false">IF(ABS(F6)&lt;=0.15,"PASS","FAIL")</f>
@@ -3754,7 +3757,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C7" s="38" t="n">
         <f aca="false">13_Energy_Use!$C$24/1000</f>
@@ -3779,11 +3782,11 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C8" s="37" t="n">
         <f aca="false">(13_Energy_Use!$C$18+13_Energy_Use!$C$24)/(i_length*i_width*i_floors)</f>
-        <v>221.616405305601</v>
+        <v>207.5598741821</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">(i_m_elec+i_m_gas)*1000/(i_length*i_width*i_floors)</f>
@@ -3791,11 +3794,11 @@
       </c>
       <c r="E8" s="43" t="n">
         <f aca="false">C8-D8</f>
-        <v>45.7637513188357</v>
+        <v>31.7072201953348</v>
       </c>
       <c r="F8" s="41" t="n">
         <f aca="false">(C8-D8)/D8</f>
-        <v>0.260239184802295</v>
+        <v>0.180305610842366</v>
       </c>
       <c r="G8" s="42" t="str">
         <f aca="false">IF(ABS(F8)&lt;=0.15,"PASS","FAIL")</f>
@@ -3804,7 +3807,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -3815,10 +3818,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>155</v>
@@ -3826,44 +3829,44 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">05_Heat_Loss!$F$30/1000</f>
         <v>258.393982722624</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">08_Heat_Balance!$C$11/1000</f>
-        <v>0</v>
+        <v>54.077702338624</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">08_Heat_Balance!$C$19/1000</f>
-        <v>456.522440710807</v>
+        <v>193.647082360807</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">05_Heat_Loss!$C$35*04_Weather!$C$14*24/1000000</f>
         <v>127.541188841472</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -7063,13 +7066,12 @@
         <f aca="false">i_occ_h</f>
         <v>1649271</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">i_pers_W*i_occ_h/1000</f>
-        <v>123695.325</v>
+      <c r="E6" s="11" t="n">
+        <v>108438</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">E6/1000</f>
-        <v>123.695325</v>
+        <v>108.438</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>322</v>
@@ -7087,13 +7089,12 @@
         <f aca="false">i_light_h</f>
         <v>4380</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <f aca="false">C7*D7/1000</f>
-        <v>151435.872</v>
+      <c r="E7" s="11" t="n">
+        <v>38268</v>
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">E7/1000</f>
-        <v>151.435872</v>
+        <v>38.268</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>324</v>
@@ -7111,21 +7112,20 @@
         <f aca="false">i_equip_h</f>
         <v>6000</v>
       </c>
-      <c r="E8" s="14" t="n">
-        <f aca="false">C8*D8/1000</f>
-        <v>388962</v>
+      <c r="E8" s="11" t="n">
+        <v>39432</v>
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">E8/1000</f>
-        <v>388.962</v>
+        <v>39.432</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>256</v>
@@ -7142,12 +7142,12 @@
         <v>8</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">09_DHW!$F$11</f>
@@ -7158,25 +7158,25 @@
         <v>53.4111111111111</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>725504.308111111</v>
+        <v>247549.111111111</v>
       </c>
       <c r="F12" s="26" t="n">
         <f aca="false">E12/1000</f>
-        <v>725.504308111111</v>
+        <v>247.549111111111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -7187,12 +7187,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C16" s="29" t="n">
         <f aca="false">i_gain_useful_h</f>
@@ -7202,25 +7202,25 @@
         <v>97</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E17" s="12" t="n">
         <f aca="false">07_Internal_Gains!$E$12*i_gain_useful_h</f>
-        <v>326476.93865</v>
+        <v>111397.1</v>
       </c>
       <c r="F17" s="26" t="n">
         <f aca="false">E17/1000</f>
-        <v>326.47693865</v>
+        <v>111.3971</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E18" s="12" t="n">
         <f aca="false">06_Heat_Gain!$F$34*0.35</f>
@@ -7231,7 +7231,7 @@
         <v>39.4457946624</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -7262,7 +7262,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7272,7 +7272,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>109</v>
@@ -7291,7 +7291,7 @@
         <v>139</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>155</v>
@@ -7299,7 +7299,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">05_Heat_Loss!$F$30</f>
@@ -7310,29 +7310,29 @@
         <v>258.393982722624</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C7" s="30" t="n">
         <f aca="false">07_Internal_Gains!$E$17</f>
-        <v>326476.93865</v>
+        <v>111397.1</v>
       </c>
       <c r="D7" s="13" t="n">
         <f aca="false">C7/1000</f>
-        <v>326.47693865</v>
+        <v>111.3971</v>
       </c>
       <c r="E7" s="31" t="n">
         <f aca="false">C7/C6</f>
-        <v>1.26348506729919</v>
+        <v>0.431113367371176</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C8" s="30" t="n">
         <f aca="false">06_Heat_Gain!$D$46</f>
@@ -7349,7 +7349,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C9" s="30" t="n">
         <f aca="false">10_Ventilation!$F$14</f>
@@ -7364,25 +7364,25 @@
         <v>0.257061637752233</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">MAX(0, C6-C7-C8-C9)</f>
-        <v>0</v>
+        <v>54077.702338624</v>
       </c>
       <c r="D11" s="26" t="n">
         <f aca="false">C11/1000</f>
-        <v>0</v>
+        <v>54.077702338624</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -7392,7 +7392,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>109</v>
@@ -7401,7 +7401,7 @@
         <v>139</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>155</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C15" s="25" t="n">
         <f aca="false">06_Heat_Gain!$F$37</f>
@@ -7422,7 +7422,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">06_Heat_Gain!$E$46</f>
@@ -7433,38 +7433,38 @@
         <v>54.779</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">07_Internal_Gains!$E$12*(1-i_gain_useful_h)</f>
-        <v>399027.369461111</v>
+        <v>136152.011111111</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">C17/1000</f>
-        <v>399.027369461111</v>
+        <v>136.152011111111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">C15+C16+C17</f>
-        <v>456522.440710807</v>
+        <v>193647.082360807</v>
       </c>
       <c r="D19" s="26" t="n">
         <f aca="false">C19/1000</f>
-        <v>456.522440710807</v>
+        <v>193.647082360807</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -7474,20 +7474,20 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C22" s="32" t="n">
         <f aca="false">C11</f>
-        <v>0</v>
+        <v>54077.702338624</v>
       </c>
       <c r="D22" s="26" t="n">
         <f aca="false">C22/1000</f>
-        <v>0</v>
+        <v>54.077702338624</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C23" s="14" t="n">
         <f aca="false">05_Heat_Loss!$C$35*04_Weather!$C$14*24/1000</f>
@@ -7498,19 +7498,19 @@
         <v>127.541188841472</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C24" s="33" t="n">
         <f aca="false">C22-C23</f>
-        <v>-127541.188841472</v>
+        <v>-73463.486502848</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
